--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>HC</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Gerente</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Director de obra</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ValidacionParametrización</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Cluster</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>HorarioIntermedia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>HorarioSemanal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ConteoIntermedia</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ConteoSemanal</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -581,24 +569,26 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -617,23 +607,23 @@
           <t>2026-03-07, 2026-03-15, 2026-03-21, 2026-03-30</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-21</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" t="n">
-        <v>2</v>
-      </c>
       <c r="W2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -670,7 +660,9 @@
           <t>MARTES</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>11</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>MIERCOLES</t>
@@ -757,24 +749,26 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -795,25 +789,25 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-25</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="X4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -847,24 +841,26 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -883,16 +879,20 @@
           <t>2026-03-17, 2026-03-24</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -611,28 +611,24 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-15, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-05, 2026-03-15, 2026-03-21, 2026-03-30</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-15, 2026-03-21, 2026-03-30</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-24</t>
-        </is>
-      </c>
+          <t>2026-03-07, 2026-03-15, 2026-03-16, 2026-03-21, 2026-03-31</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -699,7 +695,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-17</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -709,25 +705,21 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-10, 2026-03-17</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-13</t>
-        </is>
-      </c>
+          <t>2026-03-11, 2026-03-18</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -796,7 +788,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-17, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-12, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -806,20 +798,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-25</t>
+          <t>2026-03-12, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" t="n">
         <v>0.75</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -883,28 +875,28 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>2026-03-17, 2026-03-24</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-03-17, 2026-03-24</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>

--- a/output/calendario_comparado.xlsx
+++ b/output/calendario_comparado.xlsx
@@ -827,7 +827,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecución </t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
